--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127415117</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128820953</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79735</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Surtjärnen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>567045</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6719358</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Nicklas Gustavsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>128820953</v>
       </c>
       <c r="B3" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,49 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127415117</v>
+        <v>128820953</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>79946</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Korså bruk, Gstr</t>
+          <t>Surtjärnen, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566936</v>
+        <v>567045</v>
       </c>
       <c r="R2" t="n">
-        <v>6719359</v>
+        <v>6719358</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -744,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-10-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128820953</v>
+        <v>129001117</v>
       </c>
       <c r="B3" t="n">
-        <v>79660</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,17 +800,21 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Surtjärnen, Gstr</t>
+          <t>Korså bruk, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567045</v>
+        <v>567049</v>
       </c>
       <c r="R3" t="n">
-        <v>6719358</v>
+        <v>6719380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,6 +849,11 @@
           <t>2025-10-01</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -866,15 +866,232 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Nicklas Gustavsson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127415117</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korså bruk, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>566936</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6719359</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>97420706</v>
+      </c>
+      <c r="B5" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hyn, Surtjärnsviken, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566770</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6719278</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2008-06-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2008-06-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Strand, blockig, fuktig, vitmossetuvig sjöstrand mellan slutbarrskog och grund vik av sjö</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 299800N</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Bergström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gunni Hedkvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Gästriklands flora (2016)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35741-2025 artfynd.xlsx
+++ b/artfynd/A 35741-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128820953</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -981,6 +996,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127415117</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,8 +1112,19 @@
           <t>Gästriklands flora (2016)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97420706</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>